--- a/Documents/Product Catalog/Office/Sofa Specifications.xlsx
+++ b/Documents/Product Catalog/Office/Sofa Specifications.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Product Price List\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\Office\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF68574F-9C38-41D9-BC1E-97646B6AB2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sofa " sheetId="10" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Sofa '!$B$1:$R$21</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -26,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="91">
   <si>
     <t xml:space="preserve">Product Name </t>
   </si>
@@ -81,30 +84,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sofa </t>
-  </si>
-  <si>
-    <t>TFL-OSF-301 FR</t>
-  </si>
-  <si>
-    <t>TFL-OSF-302 FR</t>
-  </si>
-  <si>
-    <t>TFL-OSF-303 FR</t>
-  </si>
-  <si>
-    <t>TFL-OSF-304 FR</t>
-  </si>
-  <si>
-    <t>TFL-OSF-305 FR</t>
-  </si>
-  <si>
-    <t>TFL-OSF-306 FR</t>
-  </si>
-  <si>
-    <t>TFL-OSF-307 FR</t>
-  </si>
-  <si>
-    <t>TFL-OSF-308 FR</t>
   </si>
   <si>
     <t>2- Seater Sofa</t>
@@ -701,11 +680,59 @@
 • Products showing signs of customer misuse or damage may not qualify for return or exchange.
 • All return and exchange requests are subject to final inspection and approval by the company.</t>
   </si>
+  <si>
+    <t>Sub-Sub</t>
+  </si>
+  <si>
+    <t>TFL-OSF-302 FR-D</t>
+  </si>
+  <si>
+    <t>TFL-OSF-302 FR-S</t>
+  </si>
+  <si>
+    <t>TFL-OSF-303 FR-D</t>
+  </si>
+  <si>
+    <t>TFL-OSF-303 FR-S</t>
+  </si>
+  <si>
+    <t>TFL-OSF-304 FR-D</t>
+  </si>
+  <si>
+    <t>TFL-OSF-304 FR-S</t>
+  </si>
+  <si>
+    <t>TFL-OSF-305 FR-D</t>
+  </si>
+  <si>
+    <t>TFL-OSF-305 FR-S</t>
+  </si>
+  <si>
+    <t>TFL-OSF-306 FR-D</t>
+  </si>
+  <si>
+    <t>TFL-OSF-306 FR-S</t>
+  </si>
+  <si>
+    <t>TFL-OSF-307 FR-D</t>
+  </si>
+  <si>
+    <t>TFL-OSF-307 FR-S</t>
+  </si>
+  <si>
+    <t>TFL-OSF-308 FR-S</t>
+  </si>
+  <si>
+    <t>TFL-OSF-301 FR-S</t>
+  </si>
+  <si>
+    <t>TFL-OSF-301 FR-D</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11">
     <font>
       <sz val="10"/>
@@ -988,7 +1015,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1028,13 +1055,82 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1043,67 +1139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1143,7 +1179,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1193,7 +1229,7 @@
         <xdr:cNvPr id="61" name="image60.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000090010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000090010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1243,7 +1279,7 @@
         <xdr:cNvPr id="62" name="image61.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000091010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000091010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1293,7 +1329,7 @@
         <xdr:cNvPr id="63" name="image62.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000092010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000092010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1343,7 +1379,7 @@
         <xdr:cNvPr id="64" name="image63.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000093010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000093010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1393,7 +1429,7 @@
         <xdr:cNvPr id="65" name="image64.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000094010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000094010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1443,7 +1479,7 @@
         <xdr:cNvPr id="68" name="image66.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000098010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000098010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1493,7 +1529,7 @@
         <xdr:cNvPr id="69" name="image67.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000099010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000099010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1543,7 +1579,7 @@
         <xdr:cNvPr id="158" name="image65.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-0000F2010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000F2010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1579,9 +1615,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1619,9 +1655,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1656,7 +1692,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1691,7 +1727,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1864,7 +1900,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AT21"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -1887,90 +1923,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="32"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="18"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="34"/>
+      <c r="B2" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="20"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="28" t="s">
+      <c r="F3" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28" t="s">
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="37" t="s">
+      <c r="K3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="28" t="s">
+      <c r="L3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="28"/>
+      <c r="M3" s="23"/>
       <c r="N3" s="29"/>
       <c r="O3" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q3" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="28" t="s">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="P3" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="23" t="s">
+        <v>33</v>
       </c>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
@@ -2002,20 +2038,22 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="36"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="12"/>
+      <c r="H4" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="I4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="28"/>
-      <c r="K4" s="38"/>
+        <v>75</v>
+      </c>
+      <c r="J4" s="23"/>
+      <c r="K4" s="25"/>
       <c r="L4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2059,54 +2097,54 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="28"/>
     </row>
     <row r="6" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B6" s="13">
+      <c r="B6" s="33">
         <v>61</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="18" t="s">
+      <c r="E6" s="35"/>
+      <c r="F6" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="37" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>26</v>
+        <v>16</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>18</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L6" s="7">
         <f>M6*(1-0.1)</f>
@@ -2117,36 +2155,38 @@
         <v>0.1</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="10" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B7" s="14"/>
-      <c r="C7" s="19"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="24"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="E7" s="36"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="38"/>
       <c r="H7" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="J7" s="32"/>
       <c r="K7" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L7" s="7">
         <f t="shared" ref="L7:L21" si="0">M7*(1-0.1)</f>
@@ -2157,46 +2197,46 @@
         <v>0.1</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q7" s="10" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B8" s="13">
+      <c r="B8" s="33">
         <v>62</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>17</v>
+      <c r="C8" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="37" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>19</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" si="0"/>
@@ -2209,36 +2249,38 @@
         <v>0.1</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B9" s="14"/>
-      <c r="C9" s="19"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="14" t="s">
+        <v>77</v>
+      </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="24"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="E9" s="36"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="38"/>
       <c r="H9" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="J9" s="32"/>
       <c r="K9" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" si="0"/>
@@ -2251,46 +2293,46 @@
         <v>0.1</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="R9" s="10" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B10" s="13">
+      <c r="B10" s="33">
         <v>65</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>18</v>
+      <c r="C10" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="35"/>
+      <c r="F10" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="37" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>19</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" si="0"/>
@@ -2303,36 +2345,38 @@
         <v>0.1</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="R10" s="10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B11" s="14"/>
-      <c r="C11" s="19"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="J11" s="32"/>
       <c r="K11" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" si="0"/>
@@ -2345,46 +2389,46 @@
         <v>0.1</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B12" s="13">
+      <c r="B12" s="33">
         <v>66</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>19</v>
+      <c r="C12" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="37" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>26</v>
+        <v>16</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>18</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" si="0"/>
@@ -2395,36 +2439,38 @@
         <v>0.1</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="R12" s="10" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B13" s="14"/>
-      <c r="C13" s="19"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="E13" s="40"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="38"/>
       <c r="H13" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="J13" s="32"/>
       <c r="K13" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" si="0"/>
@@ -2435,46 +2481,46 @@
         <v>0.1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="R13" s="10" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B14" s="13">
+      <c r="B14" s="33">
         <v>67</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>20</v>
+      <c r="C14" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="F14" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="37" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>19</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L14" s="7">
         <f t="shared" si="0"/>
@@ -2487,36 +2533,38 @@
         <v>0.1</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B15" s="14"/>
-      <c r="C15" s="19"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="17"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="38"/>
       <c r="H15" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="J15" s="32"/>
       <c r="K15" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L15" s="7">
         <f t="shared" si="0"/>
@@ -2529,46 +2577,46 @@
         <v>0.1</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B16" s="13">
+      <c r="B16" s="33">
         <v>68</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="39"/>
+      <c r="F16" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="37" t="s">
         <v>14</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="21" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="J16" s="31" t="s">
+        <v>19</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="0"/>
@@ -2581,36 +2629,38 @@
         <v>0.1</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="R16" s="10" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B17" s="14"/>
-      <c r="C17" s="22"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="15" t="s">
+        <v>85</v>
+      </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="38"/>
       <c r="H17" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="J17" s="32"/>
       <c r="K17" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="0"/>
@@ -2623,46 +2673,46 @@
         <v>0.1</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="R17" s="10" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B18" s="13">
+      <c r="B18" s="33">
         <v>69</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="39"/>
+      <c r="F18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="37" t="s">
         <v>14</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="21" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="J18" s="31" t="s">
+        <v>19</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L18" s="7">
         <f t="shared" si="0"/>
@@ -2675,36 +2725,38 @@
         <v>0.1</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="R18" s="10" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="16" t="s">
+        <v>87</v>
+      </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="E19" s="40"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="38"/>
       <c r="H19" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="J19" s="32"/>
       <c r="K19" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L19" s="7">
         <f t="shared" si="0"/>
@@ -2717,44 +2769,44 @@
         <v>0.1</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B20" s="13">
+      <c r="B20" s="33">
         <v>70</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>23</v>
+      <c r="C20" s="41" t="s">
+        <v>88</v>
       </c>
       <c r="D20" s="8"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="18" t="s">
+      <c r="E20" s="39"/>
+      <c r="F20" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="37" t="s">
         <v>14</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>20</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L20" s="7">
         <f t="shared" si="0"/>
@@ -2765,36 +2817,36 @@
         <v>0.1</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
       <c r="H21" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="J21" s="38"/>
       <c r="K21" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L21" s="7">
         <f t="shared" si="0"/>
@@ -2805,20 +2857,67 @@
         <v>0.1</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="57">
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -2829,60 +2928,6 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
